--- a/source/guides/cdc/opioid-cds/ValueSet-methadone-urine-drug-screening-tests.xlsx
+++ b/source/guides/cdc/opioid-cds/ValueSet-methadone-urine-drug-screening-tests.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -28,10 +29,16 @@
     <t>http://fhir.org/guides/cdc/opioid-cds/ValueSet/methadone-urine-drug-screening-tests</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.113883.4.642.40.65.48.63</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2022.1.0</t>
+    <t>2022.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-25T18:08:12-06:00</t>
+    <t>2026-06-02T09:35:42-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -106,18 +113,21 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>parent</t>
+    <t>concept</t>
+  </si>
+  <si>
+    <t>is-a</t>
+  </si>
+  <si>
+    <t>LP15015-8</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
   </si>
   <si>
     <t>=</t>
   </si>
   <si>
-    <t>LP15015-8</t>
-  </si>
-  <si>
-    <t>SYSTEM</t>
-  </si>
-  <si>
     <t>LP7681-2</t>
   </si>
   <si>
@@ -133,15 +143,24 @@
     <t>http://loinc.org</t>
   </si>
   <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>http://loinc.org|2.82</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
     <t>System</t>
   </si>
   <si>
-    <t>version</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -154,7 +173,148 @@
     <t>Inactive</t>
   </si>
   <si>
-    <t>2.81</t>
+    <t>104627-5</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Presence] in Urine by Gas chromatography-mass spectrometry</t>
+  </si>
+  <si>
+    <t>104628-3</t>
+  </si>
+  <si>
+    <t>Methadone [Mass/volume] in Urine by Gas chromatography-mass spectrometry</t>
+  </si>
+  <si>
+    <t>16199-2</t>
+  </si>
+  <si>
+    <t>Methadone [Presence] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>16246-1</t>
+  </si>
+  <si>
+    <t>Methadone [Mass/volume] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>19550-3</t>
+  </si>
+  <si>
+    <t>Methadone [Presence] in Urine by Screen method</t>
+  </si>
+  <si>
+    <t>19552-9</t>
+  </si>
+  <si>
+    <t>Methadone cutoff [Mass/volume] in Urine for Screen method</t>
+  </si>
+  <si>
+    <t>19553-7</t>
+  </si>
+  <si>
+    <t>Methadone cutoff [Mass/volume] in Urine for Confirmatory method</t>
+  </si>
+  <si>
+    <t>33527-3</t>
+  </si>
+  <si>
+    <t>Deprecated Methadone.long acting metabolite [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>3773-9</t>
+  </si>
+  <si>
+    <t>Methadone [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>3774-7</t>
+  </si>
+  <si>
+    <t>Methadone [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>3775-4</t>
+  </si>
+  <si>
+    <t>Methadone [Mass/time] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>41466-4</t>
+  </si>
+  <si>
+    <t>Methadone/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>41858-2</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>42251-9</t>
+  </si>
+  <si>
+    <t>Methadone+Metabolite [Presence] in Urine by Screen method</t>
+  </si>
+  <si>
+    <t>50542-0</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>52958-6</t>
+  </si>
+  <si>
+    <t>Methadone [Moles/volume] in Urine</t>
+  </si>
+  <si>
+    <t>58390-6</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP)/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>58428-4</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Presence] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>58429-2</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Mass/volume] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>70147-4</t>
+  </si>
+  <si>
+    <t>Methadone [Mass/volume] in Urine by Screen method</t>
+  </si>
+  <si>
+    <t>70148-2</t>
+  </si>
+  <si>
+    <t>Methadone [Presence] in Urine by Screen method &gt;150 ng/mL</t>
+  </si>
+  <si>
+    <t>70149-0</t>
+  </si>
+  <si>
+    <t>Methadone [Presence] in Urine by Screen method &gt;300 ng/mL</t>
+  </si>
+  <si>
+    <t>77752-4</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) cutoff [Mass/volume] in Urine for Screen method</t>
+  </si>
+  <si>
+    <t>77754-0</t>
+  </si>
+  <si>
+    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) cutoff [Mass/volume] in Urine for Confirmatory method</t>
   </si>
   <si>
     <t>78770-5</t>
@@ -163,148 +323,16 @@
     <t>Methadone [Mass/volume] in Urine -- adjusted for lean body mass+urine creatinine</t>
   </si>
   <si>
-    <t>41466-4</t>
-  </si>
-  <si>
-    <t>Methadone/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>19552-9</t>
-  </si>
-  <si>
-    <t>Methadone cutoff [Mass/volume] in Urine for Screen method</t>
-  </si>
-  <si>
-    <t>19553-7</t>
-  </si>
-  <si>
-    <t>Methadone cutoff [Mass/volume] in Urine for Confirmatory method</t>
-  </si>
-  <si>
     <t>78857-0</t>
   </si>
   <si>
     <t>Methadone [Z-score] in Urine</t>
   </si>
   <si>
-    <t>52958-6</t>
-  </si>
-  <si>
-    <t>Methadone [Moles/volume] in Urine</t>
-  </si>
-  <si>
-    <t>70149-0</t>
-  </si>
-  <si>
-    <t>Methadone [Presence] in Urine by Screen method &gt;300 ng/mL</t>
-  </si>
-  <si>
-    <t>70148-2</t>
-  </si>
-  <si>
-    <t>Methadone [Presence] in Urine by Screen method &gt;150 ng/mL</t>
-  </si>
-  <si>
-    <t>19550-3</t>
-  </si>
-  <si>
-    <t>Methadone [Presence] in Urine by Screen method</t>
-  </si>
-  <si>
-    <t>16199-2</t>
-  </si>
-  <si>
-    <t>Methadone [Presence] in Urine by Confirmatory method</t>
-  </si>
-  <si>
-    <t>3773-9</t>
-  </si>
-  <si>
-    <t>Methadone [Presence] in Urine</t>
-  </si>
-  <si>
-    <t>70147-4</t>
-  </si>
-  <si>
-    <t>Methadone [Mass/volume] in Urine by Screen method</t>
-  </si>
-  <si>
-    <t>16246-1</t>
-  </si>
-  <si>
-    <t>Methadone [Mass/volume] in Urine by Confirmatory method</t>
-  </si>
-  <si>
-    <t>3774-7</t>
-  </si>
-  <si>
-    <t>Methadone [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>3775-4</t>
-  </si>
-  <si>
-    <t>Methadone [Mass/time] in 24 hour Urine</t>
-  </si>
-  <si>
-    <t>58390-6</t>
-  </si>
-  <si>
-    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP)/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>77752-4</t>
-  </si>
-  <si>
-    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) cutoff [Mass/volume] in Urine for Screen method</t>
-  </si>
-  <si>
-    <t>77754-0</t>
-  </si>
-  <si>
-    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) cutoff [Mass/volume] in Urine for Confirmatory method</t>
-  </si>
-  <si>
     <t>93495-0</t>
   </si>
   <si>
     <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Presence] in Urine by Screen method</t>
-  </si>
-  <si>
-    <t>58428-4</t>
-  </si>
-  <si>
-    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Presence] in Urine by Confirmatory method</t>
-  </si>
-  <si>
-    <t>41858-2</t>
-  </si>
-  <si>
-    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Presence] in Urine</t>
-  </si>
-  <si>
-    <t>58429-2</t>
-  </si>
-  <si>
-    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Mass/volume] in Urine by Confirmatory method</t>
-  </si>
-  <si>
-    <t>50542-0</t>
-  </si>
-  <si>
-    <t>2-Ethylidene-1,5-Dimethyl-3,3-Diphenylpyrrolidine (EDDP) [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>42251-9</t>
-  </si>
-  <si>
-    <t>Methadone+Metabolite [Presence] in Urine by Screen method</t>
-  </si>
-  <si>
-    <t>33527-3</t>
-  </si>
-  <si>
-    <t>Methadone.long acting metabolite [Mass/volume] in Urine</t>
   </si>
 </sst>
 </file>
@@ -438,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -545,15 +573,15 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>26</v>
       </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -561,6 +589,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -590,51 +626,51 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -644,605 +680,631 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>41</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>42</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>44</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
         <v>46</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
